--- a/data/availability/projects/ora/solana-east.xlsx
+++ b/data/availability/projects/ora/solana-east.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Solana East latest availability</t>
+          <t>Updated inventory for solana-east</t>
         </is>
       </c>
     </row>
@@ -577,17 +577,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -727,17 +727,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -777,17 +777,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -877,17 +877,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Core &amp; Shell / Finished</t>
+          <t>Core &amp; Shell</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Solana East Offices</t>
+          <t>Commercial Area</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1003,20 +1003,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>99</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>99 sqm</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1024,7 +1020,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1056,7 +1052,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1064,20 +1060,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>134</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>134 sqm</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1085,7 +1077,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1117,7 +1109,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1125,20 +1117,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>181</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>181 sqm</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1146,7 +1134,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1168,7 +1156,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1178,7 +1166,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1186,7 +1174,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1199,7 +1187,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1207,7 +1195,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1239,7 +1227,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1247,7 +1235,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1255,12 +1243,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Twinhouse</t>
+          <t>Twin House</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1268,7 +1256,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1300,7 +1288,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Solana East Residential</t>
+          <t>Villas</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1308,7 +1296,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finished with ACs</t>
+          <t>Fully Finished + ACs</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1316,12 +1304,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Standalone Villa V1a</t>
+          <t>V1a Villa</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1329,7 +1317,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1351,7 +1339,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1361,7 +1349,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Solana East Offices</t>
+          <t>Commercial Area</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1369,7 +1357,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Core &amp; Shell / Finished</t>
+          <t>Core &amp; Shell</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1377,12 +1365,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Office space from 57 sqm</t>
+          <t>Available Commercial/Office Space</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Landscape / City</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1390,7 +1378,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/data/availability/projects/ora/solana-east.xlsx
+++ b/data/availability/projects/ora/solana-east.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1009,7 +1009,6 @@
       <c r="G2" t="n">
         <v>99</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1020,7 +1019,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1066,7 +1065,6 @@
       <c r="G3" t="n">
         <v>134</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1077,7 +1075,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1123,7 +1121,6 @@
       <c r="G4" t="n">
         <v>181</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1134,7 +1131,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1195,7 +1192,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1256,7 +1253,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1317,7 +1314,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1339,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1378,7 +1375,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
